--- a/output/diccionario_datos.xlsx
+++ b/output/diccionario_datos.xlsx
@@ -9295,7 +9295,7 @@
         </is>
       </c>
       <c r="H194" t="n">
-        <v>54762</v>
+        <v>54802</v>
       </c>
       <c r="I194" t="n">
         <v>54856</v>
@@ -9341,7 +9341,7 @@
         </is>
       </c>
       <c r="H195" t="n">
-        <v>54762</v>
+        <v>54802</v>
       </c>
       <c r="I195" t="n">
         <v>54856</v>
@@ -9387,7 +9387,7 @@
         </is>
       </c>
       <c r="H196" t="n">
-        <v>54762</v>
+        <v>54802</v>
       </c>
       <c r="I196" t="n">
         <v>54856</v>
@@ -9433,7 +9433,7 @@
         </is>
       </c>
       <c r="H197" t="n">
-        <v>54655</v>
+        <v>54717</v>
       </c>
       <c r="I197" t="n">
         <v>54856</v>
@@ -9479,7 +9479,7 @@
         </is>
       </c>
       <c r="H198" t="n">
-        <v>54762</v>
+        <v>54802</v>
       </c>
       <c r="I198" t="n">
         <v>54856</v>
@@ -9571,7 +9571,7 @@
         </is>
       </c>
       <c r="H200" t="n">
-        <v>54762</v>
+        <v>54802</v>
       </c>
       <c r="I200" t="n">
         <v>54856</v>
@@ -9617,7 +9617,7 @@
         </is>
       </c>
       <c r="H201" t="n">
-        <v>54762</v>
+        <v>54802</v>
       </c>
       <c r="I201" t="n">
         <v>54856</v>
@@ -9663,7 +9663,7 @@
         </is>
       </c>
       <c r="H202" t="n">
-        <v>54734</v>
+        <v>54801</v>
       </c>
       <c r="I202" t="n">
         <v>54856</v>
@@ -12085,7 +12085,7 @@
         </is>
       </c>
       <c r="H255" t="n">
-        <v>54973</v>
+        <v>55014</v>
       </c>
       <c r="I255" t="n">
         <v>55014</v>
@@ -12131,7 +12131,7 @@
         </is>
       </c>
       <c r="H256" t="n">
-        <v>54973</v>
+        <v>55014</v>
       </c>
       <c r="I256" t="n">
         <v>55014</v>
@@ -12177,7 +12177,7 @@
         </is>
       </c>
       <c r="H257" t="n">
-        <v>54973</v>
+        <v>55014</v>
       </c>
       <c r="I257" t="n">
         <v>55014</v>
@@ -12223,7 +12223,7 @@
         </is>
       </c>
       <c r="H258" t="n">
-        <v>54947</v>
+        <v>55014</v>
       </c>
       <c r="I258" t="n">
         <v>55014</v>
@@ -12269,7 +12269,7 @@
         </is>
       </c>
       <c r="H259" t="n">
-        <v>54973</v>
+        <v>55014</v>
       </c>
       <c r="I259" t="n">
         <v>55014</v>
@@ -12361,7 +12361,7 @@
         </is>
       </c>
       <c r="H261" t="n">
-        <v>54973</v>
+        <v>55014</v>
       </c>
       <c r="I261" t="n">
         <v>55014</v>
@@ -12407,7 +12407,7 @@
         </is>
       </c>
       <c r="H262" t="n">
-        <v>54973</v>
+        <v>55014</v>
       </c>
       <c r="I262" t="n">
         <v>55014</v>
@@ -12453,7 +12453,7 @@
         </is>
       </c>
       <c r="H263" t="n">
-        <v>54944</v>
+        <v>55014</v>
       </c>
       <c r="I263" t="n">
         <v>55014</v>
@@ -14761,7 +14761,7 @@
         </is>
       </c>
       <c r="H315" t="n">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="I315" t="n">
         <v>417</v>
@@ -14807,7 +14807,7 @@
         </is>
       </c>
       <c r="H316" t="n">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="I316" t="n">
         <v>417</v>
@@ -14853,7 +14853,7 @@
         </is>
       </c>
       <c r="H317" t="n">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="I317" t="n">
         <v>417</v>
@@ -14899,7 +14899,7 @@
         </is>
       </c>
       <c r="H318" t="n">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="I318" t="n">
         <v>417</v>
@@ -14945,7 +14945,7 @@
         </is>
       </c>
       <c r="H319" t="n">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="I319" t="n">
         <v>417</v>
@@ -15037,7 +15037,7 @@
         </is>
       </c>
       <c r="H321" t="n">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="I321" t="n">
         <v>417</v>
@@ -15083,7 +15083,7 @@
         </is>
       </c>
       <c r="H322" t="n">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="I322" t="n">
         <v>417</v>
@@ -15129,7 +15129,7 @@
         </is>
       </c>
       <c r="H323" t="n">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="I323" t="n">
         <v>417</v>
@@ -15769,7 +15769,7 @@
         </is>
       </c>
       <c r="H337" t="n">
-        <v>1579</v>
+        <v>1585</v>
       </c>
       <c r="I337" t="n">
         <v>1585</v>
@@ -15815,7 +15815,7 @@
         </is>
       </c>
       <c r="H338" t="n">
-        <v>1579</v>
+        <v>1585</v>
       </c>
       <c r="I338" t="n">
         <v>1585</v>
@@ -15861,7 +15861,7 @@
         </is>
       </c>
       <c r="H339" t="n">
-        <v>1579</v>
+        <v>1585</v>
       </c>
       <c r="I339" t="n">
         <v>1585</v>
@@ -15907,7 +15907,7 @@
         </is>
       </c>
       <c r="H340" t="n">
-        <v>1579</v>
+        <v>1585</v>
       </c>
       <c r="I340" t="n">
         <v>1585</v>
@@ -15953,7 +15953,7 @@
         </is>
       </c>
       <c r="H341" t="n">
-        <v>1579</v>
+        <v>1585</v>
       </c>
       <c r="I341" t="n">
         <v>1585</v>
@@ -16045,7 +16045,7 @@
         </is>
       </c>
       <c r="H343" t="n">
-        <v>1579</v>
+        <v>1585</v>
       </c>
       <c r="I343" t="n">
         <v>1585</v>
@@ -16091,7 +16091,7 @@
         </is>
       </c>
       <c r="H344" t="n">
-        <v>1579</v>
+        <v>1585</v>
       </c>
       <c r="I344" t="n">
         <v>1585</v>
@@ -16137,7 +16137,7 @@
         </is>
       </c>
       <c r="H345" t="n">
-        <v>1579</v>
+        <v>1585</v>
       </c>
       <c r="I345" t="n">
         <v>1585</v>
@@ -16915,7 +16915,7 @@
         </is>
       </c>
       <c r="H362" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="I362" t="n">
         <v>116</v>
@@ -19575,7 +19575,7 @@
         </is>
       </c>
       <c r="H420" t="n">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="I420" t="n">
         <v>517</v>
@@ -19621,7 +19621,7 @@
         </is>
       </c>
       <c r="H421" t="n">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="I421" t="n">
         <v>517</v>
@@ -19667,7 +19667,7 @@
         </is>
       </c>
       <c r="H422" t="n">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="I422" t="n">
         <v>517</v>
@@ -19759,7 +19759,7 @@
         </is>
       </c>
       <c r="H424" t="n">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="I424" t="n">
         <v>517</v>
@@ -22319,7 +22319,7 @@
         </is>
       </c>
       <c r="H480" t="n">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="I480" t="n">
         <v>330</v>
@@ -22963,7 +22963,7 @@
         </is>
       </c>
       <c r="H494" t="n">
-        <v>7111</v>
+        <v>7112</v>
       </c>
       <c r="I494" t="n">
         <v>7390</v>
@@ -23009,7 +23009,7 @@
         </is>
       </c>
       <c r="H495" t="n">
-        <v>7111</v>
+        <v>7112</v>
       </c>
       <c r="I495" t="n">
         <v>7390</v>
@@ -23055,7 +23055,7 @@
         </is>
       </c>
       <c r="H496" t="n">
-        <v>7104</v>
+        <v>7106</v>
       </c>
       <c r="I496" t="n">
         <v>7390</v>
@@ -23101,7 +23101,7 @@
         </is>
       </c>
       <c r="H497" t="n">
-        <v>7111</v>
+        <v>7112</v>
       </c>
       <c r="I497" t="n">
         <v>7390</v>
@@ -23147,7 +23147,7 @@
         </is>
       </c>
       <c r="H498" t="n">
-        <v>7388</v>
+        <v>7387</v>
       </c>
       <c r="I498" t="n">
         <v>7390</v>
@@ -23193,7 +23193,7 @@
         </is>
       </c>
       <c r="H499" t="n">
-        <v>7111</v>
+        <v>7112</v>
       </c>
       <c r="I499" t="n">
         <v>7390</v>
@@ -23239,7 +23239,7 @@
         </is>
       </c>
       <c r="H500" t="n">
-        <v>7111</v>
+        <v>7112</v>
       </c>
       <c r="I500" t="n">
         <v>7390</v>
@@ -23285,7 +23285,7 @@
         </is>
       </c>
       <c r="H501" t="n">
-        <v>7108</v>
+        <v>7112</v>
       </c>
       <c r="I501" t="n">
         <v>7390</v>
@@ -27983,7 +27983,7 @@
         </is>
       </c>
       <c r="H604" t="n">
-        <v>17616</v>
+        <v>17630</v>
       </c>
       <c r="I604" t="n">
         <v>17684</v>
@@ -28029,7 +28029,7 @@
         </is>
       </c>
       <c r="H605" t="n">
-        <v>17616</v>
+        <v>17630</v>
       </c>
       <c r="I605" t="n">
         <v>17684</v>
@@ -28075,7 +28075,7 @@
         </is>
       </c>
       <c r="H606" t="n">
-        <v>17410</v>
+        <v>17431</v>
       </c>
       <c r="I606" t="n">
         <v>17684</v>
@@ -28121,7 +28121,7 @@
         </is>
       </c>
       <c r="H607" t="n">
-        <v>17616</v>
+        <v>17630</v>
       </c>
       <c r="I607" t="n">
         <v>17684</v>
@@ -28167,7 +28167,7 @@
         </is>
       </c>
       <c r="H608" t="n">
-        <v>17684</v>
+        <v>17670</v>
       </c>
       <c r="I608" t="n">
         <v>17684</v>
@@ -28259,7 +28259,7 @@
         </is>
       </c>
       <c r="H610" t="n">
-        <v>17616</v>
+        <v>17630</v>
       </c>
       <c r="I610" t="n">
         <v>17684</v>
@@ -28305,7 +28305,7 @@
         </is>
       </c>
       <c r="H611" t="n">
-        <v>17610</v>
+        <v>17629</v>
       </c>
       <c r="I611" t="n">
         <v>17684</v>
@@ -30217,7 +30217,7 @@
         </is>
       </c>
       <c r="H653" t="n">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I653" t="n">
         <v>278</v>
@@ -48641,7 +48641,7 @@
         </is>
       </c>
       <c r="H1057" t="n">
-        <v>186783</v>
+        <v>186942</v>
       </c>
       <c r="I1057" t="n">
         <v>186974</v>
@@ -48687,7 +48687,7 @@
         </is>
       </c>
       <c r="H1058" t="n">
-        <v>186783</v>
+        <v>186942</v>
       </c>
       <c r="I1058" t="n">
         <v>186974</v>
@@ -48733,7 +48733,7 @@
         </is>
       </c>
       <c r="H1059" t="n">
-        <v>186783</v>
+        <v>186942</v>
       </c>
       <c r="I1059" t="n">
         <v>186974</v>
@@ -48779,7 +48779,7 @@
         </is>
       </c>
       <c r="H1060" t="n">
-        <v>180392</v>
+        <v>180502</v>
       </c>
       <c r="I1060" t="n">
         <v>186974</v>
@@ -48825,7 +48825,7 @@
         </is>
       </c>
       <c r="H1061" t="n">
-        <v>186783</v>
+        <v>186942</v>
       </c>
       <c r="I1061" t="n">
         <v>186974</v>
@@ -48917,7 +48917,7 @@
         </is>
       </c>
       <c r="H1063" t="n">
-        <v>186783</v>
+        <v>186855</v>
       </c>
       <c r="I1063" t="n">
         <v>186974</v>
@@ -48963,7 +48963,7 @@
         </is>
       </c>
       <c r="H1064" t="n">
-        <v>186783</v>
+        <v>186855</v>
       </c>
       <c r="I1064" t="n">
         <v>186974</v>
@@ -49009,7 +49009,7 @@
         </is>
       </c>
       <c r="H1065" t="n">
-        <v>186705</v>
+        <v>186852</v>
       </c>
       <c r="I1065" t="n">
         <v>186974</v>
